--- a/Good one/3. Regression/3.1_split_data/Imbalance_table.xlsx
+++ b/Good one/3. Regression/3.1_split_data/Imbalance_table.xlsx
@@ -453,50 +453,48 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Train (1985-2007)</t>
+          <t>Train (1985-2016)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5175</v>
+        <v>7200</v>
       </c>
       <c r="C2" t="n">
-        <v>302</v>
+        <v>405</v>
       </c>
       <c r="D2" t="n">
-        <v>6.14</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Validation (2008-2010)</t>
+          <t>Validation (2017-2019)</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>675</v>
       </c>
       <c r="C3" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>9.81</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Test (2011-2021)</t>
+          <t>Test (2020-2021)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2475</v>
+        <v>450</v>
       </c>
       <c r="C4" t="n">
-        <v>43</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.87</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Good one/3. Regression/3.1_split_data/Imbalance_table.xlsx
+++ b/Good one/3. Regression/3.1_split_data/Imbalance_table.xlsx
@@ -453,48 +453,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Train (1985-2016)</t>
+          <t>Train (1985-2013)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7200</v>
+        <v>6525</v>
       </c>
       <c r="C2" t="n">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="D2" t="n">
-        <v>5.91</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Validation (2017-2019)</t>
+          <t>Validation (2014-2015)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>675</v>
+        <v>450</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Test (2020-2021)</t>
+          <t>Test (2016-2017)</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>450</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
